--- a/Team-Data/2014-15/1-14-2014-15.xlsx
+++ b/Team-Data/2014-15/1-14-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.795</v>
+        <v>0.789</v>
       </c>
       <c r="H2" t="n">
         <v>48.3</v>
@@ -679,67 +746,67 @@
         <v>37.8</v>
       </c>
       <c r="J2" t="n">
-        <v>80.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L2" t="n">
         <v>9.6</v>
       </c>
       <c r="M2" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.385</v>
+        <v>0.386</v>
       </c>
       <c r="O2" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P2" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.771</v>
+        <v>0.768</v>
       </c>
       <c r="R2" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T2" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U2" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="V2" t="n">
         <v>14.5</v>
       </c>
       <c r="W2" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.1</v>
+        <v>103</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -754,7 +821,7 @@
         <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
         <v>27</v>
@@ -769,22 +836,22 @@
         <v>8</v>
       </c>
       <c r="AN2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW2" t="n">
         <v>6</v>
@@ -802,7 +869,7 @@
         <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
@@ -814,7 +881,7 @@
         <v>7</v>
       </c>
       <c r="BC2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -843,85 +910,85 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3" t="n">
         <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>0.351</v>
+        <v>0.361</v>
       </c>
       <c r="H3" t="n">
         <v>48.7</v>
       </c>
       <c r="I3" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="J3" t="n">
-        <v>88.3</v>
+        <v>88.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M3" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.323</v>
+        <v>0.322</v>
       </c>
       <c r="O3" t="n">
         <v>15.1</v>
       </c>
       <c r="P3" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.757</v>
+        <v>0.755</v>
       </c>
       <c r="R3" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="T3" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U3" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="V3" t="n">
         <v>14.6</v>
       </c>
       <c r="W3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X3" t="n">
         <v>4.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z3" t="n">
         <v>21.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>102.3</v>
+        <v>102.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.5</v>
+        <v>-1.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
         <v>25</v>
@@ -930,7 +997,7 @@
         <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH3" t="n">
         <v>6</v>
@@ -945,13 +1012,13 @@
         <v>16</v>
       </c>
       <c r="AL3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM3" t="n">
         <v>13</v>
       </c>
       <c r="AN3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
@@ -966,7 +1033,7 @@
         <v>17</v>
       </c>
       <c r="AS3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
         <v>12</v>
@@ -975,28 +1042,28 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="n">
         <v>25</v>
       </c>
       <c r="AY3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -1025,94 +1092,94 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="n">
         <v>16</v>
       </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>0.41</v>
+        <v>0.421</v>
       </c>
       <c r="H4" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I4" t="n">
         <v>36.2</v>
       </c>
       <c r="J4" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L4" t="n">
         <v>6.8</v>
       </c>
       <c r="M4" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.323</v>
+        <v>0.321</v>
       </c>
       <c r="O4" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="P4" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.751</v>
+        <v>0.75</v>
       </c>
       <c r="R4" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T4" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="U4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
       </c>
       <c r="X4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y4" t="n">
         <v>4.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
@@ -1121,25 +1188,25 @@
         <v>25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK4" t="n">
         <v>19</v>
       </c>
       <c r="AL4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
         <v>16</v>
       </c>
       <c r="AN4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ4" t="n">
         <v>17</v>
@@ -1148,13 +1215,13 @@
         <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU4" t="n">
         <v>20</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>23</v>
       </c>
       <c r="AV4" t="n">
         <v>20</v>
@@ -1163,13 +1230,13 @@
         <v>21</v>
       </c>
       <c r="AX4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
         <v>21</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5" t="n">
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>0.375</v>
+        <v>0.385</v>
       </c>
       <c r="H5" t="n">
         <v>48.8</v>
@@ -1225,40 +1292,40 @@
         <v>36.4</v>
       </c>
       <c r="J5" t="n">
-        <v>84.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.429</v>
+        <v>0.431</v>
       </c>
       <c r="L5" t="n">
         <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N5" t="n">
         <v>0.313</v>
       </c>
       <c r="O5" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="P5" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.741</v>
+        <v>0.744</v>
       </c>
       <c r="R5" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
         <v>33.1</v>
       </c>
       <c r="T5" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U5" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V5" t="n">
         <v>11.9</v>
@@ -1267,25 +1334,25 @@
         <v>5.7</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Z5" t="n">
         <v>18.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3</v>
+        <v>-2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1300,7 +1367,7 @@
         <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ5" t="n">
         <v>11</v>
@@ -1312,19 +1379,19 @@
         <v>27</v>
       </c>
       <c r="AM5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN5" t="n">
         <v>29</v>
       </c>
       <c r="AO5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP5" t="n">
         <v>16</v>
       </c>
-      <c r="AP5" t="n">
-        <v>15</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AR5" t="n">
         <v>23</v>
@@ -1333,10 +1400,10 @@
         <v>9</v>
       </c>
       <c r="AT5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1345,10 +1412,10 @@
         <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -1389,64 +1456,64 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" t="n">
         <v>26</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.65</v>
+        <v>0.667</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>0.444</v>
       </c>
       <c r="L6" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M6" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.358</v>
+        <v>0.354</v>
       </c>
       <c r="O6" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="P6" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0.778</v>
       </c>
       <c r="R6" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S6" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="T6" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="U6" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V6" t="n">
         <v>14.5</v>
       </c>
       <c r="W6" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X6" t="n">
         <v>6.7</v>
@@ -1455,28 +1522,28 @@
         <v>5.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
+        <v>102.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
         <v>13</v>
@@ -1491,13 +1558,13 @@
         <v>20</v>
       </c>
       <c r="AL6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM6" t="n">
         <v>17</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1509,19 +1576,19 @@
         <v>5</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
         <v>7</v>
       </c>
       <c r="AT6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU6" t="n">
         <v>13</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
         <v>28</v>
@@ -1533,7 +1600,7 @@
         <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>14</v>
@@ -1661,7 +1728,7 @@
         <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>22</v>
@@ -1679,13 +1746,13 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
         <v>12</v>
@@ -1694,7 +1761,7 @@
         <v>15</v>
       </c>
       <c r="AS7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT7" t="n">
         <v>24</v>
@@ -1706,7 +1773,7 @@
         <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX7" t="n">
         <v>26</v>
@@ -1718,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
         <v>17</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -1771,19 +1838,19 @@
         <v>41.1</v>
       </c>
       <c r="J8" t="n">
-        <v>87.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.472</v>
+        <v>0.474</v>
       </c>
       <c r="L8" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>27</v>
+        <v>26.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.354</v>
+        <v>0.359</v>
       </c>
       <c r="O8" t="n">
         <v>17.2</v>
@@ -1795,16 +1862,16 @@
         <v>0.76</v>
       </c>
       <c r="R8" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T8" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
         <v>12.1</v>
@@ -1813,73 +1880,73 @@
         <v>8.1</v>
       </c>
       <c r="X8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AD8" t="n">
         <v>5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>109</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK8" t="n">
         <v>2</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>4</v>
       </c>
       <c r="AL8" t="n">
         <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP8" t="n">
         <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -1891,13 +1958,13 @@
         <v>11</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
         <v>3</v>
@@ -1906,7 +1973,7 @@
         <v>2</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" t="n">
         <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>0.474</v>
+        <v>0.459</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1953,40 +2020,40 @@
         <v>37.9</v>
       </c>
       <c r="J9" t="n">
-        <v>86.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="L9" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M9" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.32</v>
+        <v>0.322</v>
       </c>
       <c r="O9" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>25.9</v>
+        <v>25.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.743</v>
+        <v>0.741</v>
       </c>
       <c r="R9" t="n">
         <v>12.6</v>
       </c>
       <c r="S9" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="T9" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="U9" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V9" t="n">
         <v>14.7</v>
@@ -1995,28 +2062,28 @@
         <v>6.9</v>
       </c>
       <c r="X9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y9" t="n">
         <v>6</v>
       </c>
       <c r="Z9" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.6</v>
+        <v>102.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>16</v>
@@ -2025,7 +2092,7 @@
         <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
         <v>12</v>
@@ -2034,16 +2101,16 @@
         <v>5</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AM9" t="n">
         <v>12</v>
       </c>
       <c r="AN9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
         <v>4</v>
@@ -2052,22 +2119,22 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
         <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2082,13 +2149,13 @@
         <v>30</v>
       </c>
       <c r="BA9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB9" t="n">
         <v>9</v>
       </c>
-      <c r="BB9" t="n">
-        <v>8</v>
-      </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -2117,34 +2184,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10" t="n">
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>0.359</v>
+        <v>0.368</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J10" t="n">
-        <v>85.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.427</v>
+        <v>0.426</v>
       </c>
       <c r="L10" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M10" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="N10" t="n">
         <v>0.345</v>
@@ -2156,64 +2223,64 @@
         <v>22.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="S10" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="T10" t="n">
-        <v>45.3</v>
+        <v>45.7</v>
       </c>
       <c r="U10" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V10" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="W10" t="n">
         <v>7.7</v>
       </c>
       <c r="X10" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y10" t="n">
         <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>97.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF10" t="n">
         <v>22</v>
       </c>
       <c r="AG10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
         <v>20</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
         <v>29</v>
@@ -2222,7 +2289,7 @@
         <v>9</v>
       </c>
       <c r="AM10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN10" t="n">
         <v>19</v>
@@ -2231,13 +2298,13 @@
         <v>25</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
       </c>
       <c r="AR10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS10" t="n">
         <v>10</v>
@@ -2252,16 +2319,16 @@
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.861</v>
+        <v>0.857</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="J11" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0.484</v>
@@ -2329,7 +2396,7 @@
         <v>26.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.385</v>
+        <v>0.383</v>
       </c>
       <c r="O11" t="n">
         <v>16.6</v>
@@ -2344,19 +2411,19 @@
         <v>9.9</v>
       </c>
       <c r="S11" t="n">
-        <v>34.6</v>
+        <v>34.8</v>
       </c>
       <c r="T11" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="U11" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="V11" t="n">
         <v>15.2</v>
       </c>
       <c r="W11" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X11" t="n">
         <v>6.4</v>
@@ -2365,16 +2432,16 @@
         <v>3.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA11" t="n">
         <v>18.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>109.3</v>
+        <v>109.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
         <v>30</v>
@@ -2395,25 +2462,25 @@
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
       </c>
       <c r="AL11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO11" t="n">
         <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
@@ -2431,10 +2498,10 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX11" t="n">
         <v>2</v>
@@ -2446,7 +2513,7 @@
         <v>11</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -2484,97 +2551,97 @@
         <v>38</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>36.5</v>
+        <v>36.2</v>
       </c>
       <c r="J12" t="n">
-        <v>83.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.438</v>
+        <v>0.436</v>
       </c>
       <c r="L12" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="M12" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="N12" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O12" t="n">
-        <v>17.1</v>
+        <v>17.5</v>
       </c>
       <c r="P12" t="n">
-        <v>24.1</v>
+        <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.712</v>
+        <v>0.707</v>
       </c>
       <c r="R12" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S12" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="U12" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V12" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="W12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y12" t="n">
         <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>101.9</v>
+        <v>101.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ12" t="n">
         <v>16</v>
@@ -2592,25 +2659,25 @@
         <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2619,16 +2686,16 @@
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -2747,10 +2814,10 @@
         <v>21</v>
       </c>
       <c r="AF13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG13" t="n">
         <v>22</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>21</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
@@ -2759,13 +2826,13 @@
         <v>27</v>
       </c>
       <c r="AJ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
@@ -2774,10 +2841,10 @@
         <v>22</v>
       </c>
       <c r="AO13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP13" t="n">
         <v>22</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>21</v>
       </c>
       <c r="AQ13" t="n">
         <v>19</v>
@@ -2801,13 +2868,13 @@
         <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>18</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>17</v>
       </c>
       <c r="BA13" t="n">
         <v>11</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -2845,94 +2912,94 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.667</v>
+        <v>0.658</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J14" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K14" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L14" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="M14" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="O14" t="n">
         <v>18.8</v>
       </c>
       <c r="P14" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.755</v>
+        <v>0.752</v>
       </c>
       <c r="R14" t="n">
         <v>8.6</v>
       </c>
       <c r="S14" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T14" t="n">
         <v>40.9</v>
       </c>
       <c r="U14" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="V14" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="W14" t="n">
         <v>7.7</v>
       </c>
       <c r="X14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y14" t="n">
         <v>2.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.2</v>
+        <v>106.4</v>
       </c>
       <c r="AC14" t="n">
         <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF14" t="n">
         <v>9</v>
       </c>
       <c r="AG14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2941,25 +3008,25 @@
         <v>9</v>
       </c>
       <c r="AJ14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>2</v>
       </c>
       <c r="AM14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO14" t="n">
         <v>6</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
         <v>16</v>
@@ -2977,10 +3044,10 @@
         <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
         <v>14</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" t="n">
-        <v>0.316</v>
+        <v>0.308</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>37.9</v>
+        <v>37.6</v>
       </c>
       <c r="J15" t="n">
-        <v>86.7</v>
+        <v>86.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.437</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M15" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="N15" t="n">
         <v>0.351</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="R15" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T15" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="U15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V15" t="n">
         <v>12.5</v>
@@ -3087,49 +3154,49 @@
         <v>7.4</v>
       </c>
       <c r="X15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y15" t="n">
         <v>4.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>101</v>
+        <v>100.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.7</v>
+        <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
       </c>
       <c r="AH15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI15" t="n">
         <v>15</v>
       </c>
-      <c r="AI15" t="n">
-        <v>13</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AM15" t="n">
         <v>22</v>
@@ -3138,34 +3205,34 @@
         <v>15</v>
       </c>
       <c r="AO15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
         <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
         <v>19</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY15" t="n">
         <v>8</v>
@@ -3174,7 +3241,7 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
         <v>16</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" t="n">
         <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>0.711</v>
+        <v>0.703</v>
       </c>
       <c r="H16" t="n">
         <v>49.2</v>
@@ -3239,64 +3306,64 @@
         <v>16</v>
       </c>
       <c r="N16" t="n">
-        <v>0.353</v>
+        <v>0.358</v>
       </c>
       <c r="O16" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P16" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0.774</v>
       </c>
       <c r="R16" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S16" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T16" t="n">
         <v>42.4</v>
       </c>
       <c r="U16" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W16" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z16" t="n">
         <v>19.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB16" t="n">
         <v>101.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH16" t="n">
         <v>1</v>
@@ -3317,7 +3384,7 @@
         <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO16" t="n">
         <v>9</v>
@@ -3335,7 +3402,7 @@
         <v>16</v>
       </c>
       <c r="AT16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU16" t="n">
         <v>10</v>
@@ -3344,7 +3411,7 @@
         <v>7</v>
       </c>
       <c r="AW16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX16" t="n">
         <v>22</v>
@@ -3356,7 +3423,7 @@
         <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB16" t="n">
         <v>14</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -3391,64 +3458,64 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E17" t="n">
         <v>17</v>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.436</v>
+        <v>0.447</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="J17" t="n">
-        <v>74.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L17" t="n">
         <v>7.2</v>
       </c>
       <c r="M17" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N17" t="n">
         <v>0.346</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P17" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.735</v>
+        <v>0.732</v>
       </c>
       <c r="R17" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="S17" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T17" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="U17" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V17" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X17" t="n">
         <v>4</v>
@@ -3463,16 +3530,16 @@
         <v>20.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-4.1</v>
+        <v>-3.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF17" t="n">
         <v>18</v>
@@ -3493,19 +3560,19 @@
         <v>11</v>
       </c>
       <c r="AL17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
         <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>26</v>
@@ -3514,7 +3581,7 @@
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3523,10 +3590,10 @@
         <v>27</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX17" t="n">
         <v>28</v>
@@ -3535,10 +3602,10 @@
         <v>7</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>13</v>
@@ -3663,7 +3730,7 @@
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
         <v>14</v>
@@ -3672,13 +3739,13 @@
         <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL18" t="n">
         <v>22</v>
       </c>
       <c r="AM18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN18" t="n">
         <v>8</v>
@@ -3708,7 +3775,7 @@
         <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
         <v>19</v>
@@ -3717,7 +3784,7 @@
         <v>13</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA18" t="n">
         <v>22</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-9.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
       </c>
       <c r="AF19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG19" t="n">
         <v>29</v>
@@ -3854,7 +3921,7 @@
         <v>8</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3872,13 +3939,13 @@
         <v>4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT19" t="n">
         <v>27</v>
@@ -3887,22 +3954,22 @@
         <v>11</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
         <v>5</v>
       </c>
       <c r="AX19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY19" t="n">
         <v>28</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
         <v>20</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -3955,49 +4022,49 @@
         <v>38.6</v>
       </c>
       <c r="J20" t="n">
-        <v>83.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.347</v>
+        <v>0.344</v>
       </c>
       <c r="O20" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P20" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.771</v>
+        <v>0.759</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
         <v>31.8</v>
       </c>
       <c r="T20" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="U20" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W20" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,16 +4073,16 @@
         <v>19.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="n">
-        <v>101.4</v>
+        <v>101.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
         <v>15</v>
@@ -4033,10 +4100,10 @@
         <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
@@ -4045,25 +4112,25 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP20" t="n">
         <v>17</v>
       </c>
-      <c r="AO20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP20" t="n">
+      <c r="AQ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS20" t="n">
         <v>18</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AT20" t="n">
         <v>10</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
@@ -4072,10 +4139,10 @@
         <v>6</v>
       </c>
       <c r="AW20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>27</v>
@@ -4084,7 +4151,7 @@
         <v>7</v>
       </c>
       <c r="BA20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB20" t="n">
         <v>15</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4282,7 @@
         <v>26</v>
       </c>
       <c r="AJ21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
         <v>21</v>
@@ -4227,7 +4294,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4248,7 +4315,7 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>0.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
         <v>15</v>
@@ -4394,25 +4461,25 @@
         <v>14</v>
       </c>
       <c r="AI22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM22" t="n">
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP22" t="n">
         <v>12</v>
@@ -4421,7 +4488,7 @@
         <v>21</v>
       </c>
       <c r="AR22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4433,22 +4500,22 @@
         <v>30</v>
       </c>
       <c r="AV22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW22" t="n">
         <v>23</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>14</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -4486,109 +4553,109 @@
         <v>41</v>
       </c>
       <c r="E23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
-        <v>0.366</v>
+        <v>0.341</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>37</v>
+        <v>36.7</v>
       </c>
       <c r="J23" t="n">
-        <v>81.2</v>
+        <v>81</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.453</v>
       </c>
       <c r="L23" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>19.3</v>
+        <v>18.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.368</v>
+        <v>0.369</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="P23" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.729</v>
+        <v>0.724</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>31.7</v>
+        <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>40.4</v>
+        <v>40.8</v>
       </c>
       <c r="U23" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V23" t="n">
         <v>14.6</v>
       </c>
       <c r="W23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="X23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AA23" t="n">
         <v>18.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>-4.9</v>
+        <v>-5.4</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG23" t="n">
         <v>25</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>23</v>
       </c>
       <c r="AH23" t="n">
         <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AN23" t="n">
         <v>7</v>
@@ -4606,7 +4673,7 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
@@ -4615,22 +4682,22 @@
         <v>24</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AX23" t="n">
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
         <v>19</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB23" t="n">
         <v>27</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G24" t="n">
-        <v>0.184</v>
+        <v>0.189</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,43 +4750,43 @@
         <v>33.2</v>
       </c>
       <c r="J24" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K24" t="n">
-        <v>0.41</v>
+        <v>0.411</v>
       </c>
       <c r="L24" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M24" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.298</v>
+        <v>0.301</v>
       </c>
       <c r="O24" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P24" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.678</v>
+        <v>0.68</v>
       </c>
       <c r="R24" t="n">
         <v>11.6</v>
       </c>
       <c r="S24" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T24" t="n">
         <v>41.9</v>
       </c>
       <c r="U24" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V24" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="W24" t="n">
         <v>9.9</v>
@@ -4728,22 +4795,22 @@
         <v>5.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z24" t="n">
         <v>21.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>90.3</v>
+        <v>90.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>-12.7</v>
+        <v>-12.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4755,7 +4822,7 @@
         <v>28</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>30</v>
@@ -4767,7 +4834,7 @@
         <v>30</v>
       </c>
       <c r="AL24" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AM24" t="n">
         <v>11</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
@@ -4788,13 +4855,13 @@
         <v>8</v>
       </c>
       <c r="AS24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT24" t="n">
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4803,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
         <v>23</v>
@@ -4812,7 +4879,7 @@
         <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -4943,10 +5010,10 @@
         <v>4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
         <v>5</v>
@@ -4961,7 +5028,7 @@
         <v>15</v>
       </c>
       <c r="AP25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ25" t="n">
         <v>1</v>
@@ -4970,7 +5037,7 @@
         <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
         <v>19</v>
@@ -4985,13 +5052,13 @@
         <v>7</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E26" t="n">
         <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G26" t="n">
-        <v>0.769</v>
+        <v>0.789</v>
       </c>
       <c r="H26" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I26" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J26" t="n">
         <v>86.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L26" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="M26" t="n">
         <v>27.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="O26" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P26" t="n">
         <v>19.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.791</v>
+        <v>0.788</v>
       </c>
       <c r="R26" t="n">
         <v>11.1</v>
@@ -5077,7 +5144,7 @@
         <v>35.4</v>
       </c>
       <c r="T26" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="U26" t="n">
         <v>22.9</v>
@@ -5089,7 +5156,7 @@
         <v>6.6</v>
       </c>
       <c r="X26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y26" t="n">
         <v>3.5</v>
@@ -5101,22 +5168,22 @@
         <v>19.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>103.5</v>
+        <v>103.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
         <v>7</v>
@@ -5125,13 +5192,13 @@
         <v>6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK26" t="n">
         <v>17</v>
       </c>
       <c r="AL26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM26" t="n">
         <v>2</v>
@@ -5170,7 +5237,7 @@
         <v>8</v>
       </c>
       <c r="AY26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-1.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>19</v>
       </c>
       <c r="AF27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG27" t="n">
         <v>19</v>
@@ -5304,13 +5371,13 @@
         <v>3</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ27" t="n">
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5334,13 +5401,13 @@
         <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
       </c>
       <c r="AU27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
@@ -5364,7 +5431,7 @@
         <v>10</v>
       </c>
       <c r="BC27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -5411,25 +5478,25 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.462</v>
+        <v>0.465</v>
       </c>
       <c r="L28" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.369</v>
+        <v>0.373</v>
       </c>
       <c r="O28" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P28" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q28" t="n">
         <v>0.757</v>
@@ -5438,40 +5505,40 @@
         <v>9.699999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>34</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U28" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
         <v>7.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.9</v>
+        <v>102</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5492,10 +5559,10 @@
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>15</v>
@@ -5504,7 +5571,7 @@
         <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
         <v>20</v>
@@ -5516,31 +5583,31 @@
         <v>25</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AW28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
       </c>
       <c r="AY28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB28" t="n">
         <v>12</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
         <v>12</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.676</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
@@ -5593,76 +5660,76 @@
         <v>39.4</v>
       </c>
       <c r="J29" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.462</v>
       </c>
       <c r="L29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M29" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="N29" t="n">
         <v>0.361</v>
       </c>
       <c r="O29" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P29" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.78</v>
+        <v>0.783</v>
       </c>
       <c r="R29" t="n">
         <v>11.3</v>
       </c>
       <c r="S29" t="n">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U29" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V29" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="W29" t="n">
         <v>7.2</v>
       </c>
       <c r="X29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AA29" t="n">
         <v>22</v>
       </c>
       <c r="AB29" t="n">
-        <v>107.6</v>
+        <v>107.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH29" t="n">
         <v>11</v>
@@ -5671,7 +5738,7 @@
         <v>5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK29" t="n">
         <v>10</v>
@@ -5701,22 +5768,22 @@
         <v>25</v>
       </c>
       <c r="AT29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU29" t="n">
         <v>15</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX29" t="n">
         <v>20</v>
       </c>
-      <c r="AX29" t="n">
-        <v>21</v>
-      </c>
       <c r="AY29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ29" t="n">
         <v>22</v>
@@ -5728,7 +5795,7 @@
         <v>3</v>
       </c>
       <c r="BC29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
@@ -5856,7 +5923,7 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL30" t="n">
         <v>23</v>
@@ -5868,7 +5935,7 @@
         <v>24</v>
       </c>
       <c r="AO30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP30" t="n">
         <v>13</v>
@@ -5877,7 +5944,7 @@
         <v>18</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5886,16 +5953,16 @@
         <v>16</v>
       </c>
       <c r="AU30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW30" t="n">
         <v>25</v>
       </c>
       <c r="AX30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F31" t="n">
         <v>12</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H31" t="n">
         <v>48.4</v>
@@ -5957,10 +6024,10 @@
         <v>38.9</v>
       </c>
       <c r="J31" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L31" t="n">
         <v>6.1</v>
@@ -5969,16 +6036,16 @@
         <v>15.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.392</v>
+        <v>0.394</v>
       </c>
       <c r="O31" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="P31" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="R31" t="n">
         <v>10.4</v>
@@ -5990,46 +6057,46 @@
         <v>42.9</v>
       </c>
       <c r="U31" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="V31" t="n">
         <v>14.6</v>
       </c>
       <c r="W31" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X31" t="n">
         <v>5.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="n">
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG31" t="n">
         <v>7</v>
       </c>
-      <c r="AE31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>5</v>
-      </c>
       <c r="AH31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI31" t="n">
         <v>8</v>
@@ -6038,7 +6105,7 @@
         <v>19</v>
       </c>
       <c r="AK31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL31" t="n">
         <v>26</v>
@@ -6050,13 +6117,13 @@
         <v>1</v>
       </c>
       <c r="AO31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP31" t="n">
         <v>25</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AQ31" t="n">
         <v>24</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>23</v>
       </c>
       <c r="AR31" t="n">
         <v>21</v>
@@ -6071,10 +6138,10 @@
         <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>9</v>
@@ -6083,10 +6150,10 @@
         <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB31" t="n">
         <v>18</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-14-2014-15</t>
+          <t>2015-01-14</t>
         </is>
       </c>
     </row>
